--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -6281,7 +6281,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="2" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
     <oddFooter>&amp;L&amp;16 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010&amp;R&amp;16 Tiempo de retención en el punto de origen: 3 años_x000a_Tiempo de retención en archivo muerto: N/A_x000a_Medio de registro :Electrónico</oddFooter>
@@ -12187,7 +12187,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="1.6975" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="4" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
     <oddFooter>&amp;L&amp;14 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010&amp;RTiempo de retención en el punto de origen: 3 años_x000a_Tiempo de retención en archivo muerto: N/A_x000a_Medio de registro :Electrónico</oddFooter>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -6281,7 +6281,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="2" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
     <oddFooter>&amp;L&amp;16 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010&amp;R&amp;16 Tiempo de retención en el punto de origen: 3 años_x000a_Tiempo de retención en archivo muerto: N/A_x000a_Medio de registro :Electrónico</oddFooter>
@@ -12187,7 +12187,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="1.6975" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="4" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="2" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
     <oddFooter>&amp;L&amp;14 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010&amp;RTiempo de retención en el punto de origen: 3 años_x000a_Tiempo de retención en archivo muerto: N/A_x000a_Medio de registro :Electrónico</oddFooter>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -6281,7 +6281,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
     <oddFooter>&amp;L&amp;16 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010&amp;R&amp;16 Tiempo de retención en el punto de origen: 3 años_x000a_Tiempo de retención en archivo muerto: N/A_x000a_Medio de registro :Electrónico</oddFooter>
@@ -6290,9 +6290,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="38" min="0" max="22" man="1"/>
-  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -12187,7 +12184,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="1.6975" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="2" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="2" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
     <oddFooter>&amp;L&amp;14 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010&amp;RTiempo de retención en el punto de origen: 3 años_x000a_Tiempo de retención en archivo muerto: N/A_x000a_Medio de registro :Electrónico</oddFooter>
@@ -12196,10 +12193,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="57" min="0" max="22" man="1"/>
-    <brk id="107" min="0" max="22" man="1"/>
-  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -1784,7 +1784,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1828,7 +1828,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1877,7 +1877,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1921,7 +1921,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1967,7 +1967,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -2004,16 +2004,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2025,79 +2022,20 @@
       <row>70</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="4953000" cy="2781300"/>
+    <ext cx="4953000" cy="3971925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>95250</colOff>
-      <row>80</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="6915150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>95250</colOff>
-      <row>80</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="5876925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2112,20 +2050,17 @@
     <ext cx="4953000" cy="6915150"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2140,20 +2075,17 @@
     <ext cx="4953000" cy="4800600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2165,23 +2097,20 @@
       <row>98</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="4953000" cy="3648075"/>
+    <ext cx="4953000" cy="2781300"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2193,23 +2122,20 @@
       <row>98</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="4953000" cy="5762625"/>
+    <ext cx="4953000" cy="5876925"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -1784,7 +1784,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1828,7 +1828,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1877,7 +1877,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1921,7 +1921,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1967,7 +1967,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -2004,13 +2004,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2029,13 +2032,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2105,31 +2111,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>95250</colOff>
-      <row>98</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="5876925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -1784,7 +1784,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1828,7 +1828,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1877,7 +1877,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1921,7 +1921,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1967,7 +1967,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1997,23 +1997,20 @@
       <row>70</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="4953000" cy="6496050"/>
+    <ext cx="4953000" cy="6915150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2025,23 +2022,45 @@
       <row>70</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="4953000" cy="3971925"/>
+    <ext cx="4953000" cy="4800600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>95250</colOff>
+      <row>80</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <ext cx="4953000" cy="2781300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2056,11 +2075,11 @@
     <ext cx="4953000" cy="6915150"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2081,11 +2100,11 @@
     <ext cx="4953000" cy="4800600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2106,11 +2125,11 @@
     <ext cx="4953000" cy="2781300"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -1784,7 +1784,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1828,7 +1828,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1877,7 +1877,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1921,7 +1921,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1967,7 +1967,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1997,182 +1997,14 @@
       <row>70</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="4953000" cy="6915150"/>
+    <ext cx="4381500" cy="5838825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>95250</colOff>
-      <row>70</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="4800600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>95250</colOff>
-      <row>80</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="2781300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>95250</colOff>
-      <row>90</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="6915150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>95250</colOff>
-      <row>90</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="4800600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>95250</colOff>
-      <row>98</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="2781300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>95250</colOff>
-      <row>80</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="4953000" cy="4905375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2187,17 +2019,92 @@
     <from>
       <col>11</col>
       <colOff>95250</colOff>
+      <row>70</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <ext cx="4381500" cy="6019800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>95250</colOff>
+      <row>90</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <ext cx="4381500" cy="6115050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>95250</colOff>
+      <row>90</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <ext cx="4381500" cy="4248150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>95250</colOff>
       <row>98</row>
       <rowOff>95250</rowOff>
     </from>
-    <ext cx="4953000" cy="3733800"/>
+    <ext cx="4381500" cy="2457450"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -291,6 +291,9 @@
       <color rgb="FF00B0F0"/>
       <sz val="14"/>
     </font>
+    <font>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -318,7 +321,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -495,6 +498,10 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -503,7 +510,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="418">
+  <cellXfs count="423">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1702,6 +1709,19 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1784,7 +1804,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1828,7 +1848,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1877,7 +1897,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1921,7 +1941,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1967,7 +1987,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="34082" t="29556" r="36328" b="57813"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -2004,13 +2024,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2029,13 +2052,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2054,13 +2080,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2079,13 +2108,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2104,13 +2136,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -11757,18 +11792,31 @@
     </row>
     <row r="152" ht="49.5" customHeight="1">
       <c r="A152" s="68" t="n"/>
-      <c r="B152" s="227" t="n"/>
+      <c r="B152" s="418" t="inlineStr">
+        <is>
+          <t>1  Responsable SME de Ingenieria 
+SME responsable</t>
+        </is>
+      </c>
       <c r="E152" s="90" t="n"/>
-      <c r="F152" s="90" t="n"/>
-      <c r="H152" s="90" t="n"/>
-      <c r="I152" s="90" t="n"/>
-      <c r="J152" s="90" t="n"/>
-      <c r="K152" s="90" t="n"/>
-      <c r="L152" s="90" t="n"/>
-      <c r="M152" s="90" t="n"/>
-      <c r="N152" s="90" t="n"/>
-      <c r="O152" s="90" t="n"/>
-      <c r="Q152" s="344" t="n"/>
+      <c r="F152" s="418" t="inlineStr">
+        <is>
+          <t>2  Responsable del Equipo 
+Equipment responsable</t>
+        </is>
+      </c>
+      <c r="I152" s="418" t="inlineStr">
+        <is>
+          <t>3  Representantes de EHS
+EHS Representatives</t>
+        </is>
+      </c>
+      <c r="Q152" s="418" t="inlineStr">
+        <is>
+          <t>4  Responsable del área
+Area responsable</t>
+        </is>
+      </c>
       <c r="V152" s="90" t="n"/>
       <c r="W152" s="90" t="n"/>
     </row>
@@ -11827,16 +11875,17 @@
     </row>
     <row r="157" ht="21" customHeight="1">
       <c r="A157" s="68" t="n"/>
-      <c r="F157" s="75" t="n"/>
-      <c r="G157" s="252" t="n"/>
-      <c r="H157" s="252" t="n"/>
-      <c r="I157" s="252" t="n"/>
-      <c r="J157" s="252" t="n"/>
-      <c r="K157" s="252" t="n"/>
-      <c r="L157" s="252" t="n"/>
-      <c r="M157" s="252" t="n"/>
-      <c r="N157" s="252" t="n"/>
-      <c r="O157" s="252" t="n"/>
+      <c r="F157" s="419" t="n"/>
+      <c r="G157" s="420" t="n"/>
+      <c r="H157" s="420" t="n"/>
+      <c r="I157" s="420" t="n"/>
+      <c r="J157" s="420" t="n"/>
+      <c r="K157" s="420" t="n"/>
+      <c r="L157" s="420" t="n"/>
+      <c r="M157" s="420" t="n"/>
+      <c r="N157" s="420" t="n"/>
+      <c r="O157" s="420" t="n"/>
+      <c r="P157" s="422" t="n"/>
       <c r="R157" s="75" t="n"/>
       <c r="S157" s="75" t="n"/>
       <c r="V157" s="92" t="n"/>
@@ -11854,14 +11903,18 @@
       <c r="C158" s="388" t="n"/>
       <c r="D158" s="388" t="n"/>
       <c r="E158" s="93" t="n"/>
-      <c r="F158" s="93" t="n"/>
-      <c r="G158" s="93" t="n"/>
-      <c r="H158" s="93" t="n"/>
-      <c r="I158" s="93" t="n"/>
-      <c r="J158" s="93" t="n"/>
-      <c r="K158" s="93" t="n"/>
-      <c r="L158" s="93" t="n"/>
-      <c r="M158" s="93" t="n"/>
+      <c r="F158" s="421" t="inlineStr">
+        <is>
+          <t>Nombre, Firma y Fecha 
+Name, Signature and Date</t>
+        </is>
+      </c>
+      <c r="I158" s="421" t="inlineStr">
+        <is>
+          <t>Nombre, Firma y Fecha 
+Name, Signature and Date</t>
+        </is>
+      </c>
       <c r="Q158" s="337" t="inlineStr">
         <is>
           <t>Nombre, Firma y Fecha 
@@ -11901,7 +11954,7 @@
       <c r="U163" s="227" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="180">
+  <mergeCells count="184">
     <mergeCell ref="Q158:U158"/>
     <mergeCell ref="B146:N146"/>
     <mergeCell ref="O27:U27"/>
@@ -11918,6 +11971,7 @@
     <mergeCell ref="Q4:U4"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="V16:AA16"/>
+    <mergeCell ref="F152:H152"/>
     <mergeCell ref="N124:P124"/>
     <mergeCell ref="O136:U136"/>
     <mergeCell ref="O36:U36"/>
@@ -11984,12 +12038,14 @@
     <mergeCell ref="O22:U22"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="R68:V68"/>
+    <mergeCell ref="F158:H158"/>
     <mergeCell ref="O50:U50"/>
     <mergeCell ref="AC78:AH78"/>
     <mergeCell ref="X91:AC91"/>
     <mergeCell ref="B152:D152"/>
     <mergeCell ref="O46:U46"/>
     <mergeCell ref="R61:V61"/>
+    <mergeCell ref="I158:P158"/>
     <mergeCell ref="L68:Q68"/>
     <mergeCell ref="V19:AA19"/>
     <mergeCell ref="O48:U48"/>
@@ -12062,6 +12118,7 @@
     <mergeCell ref="G136:M136"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="F62:J62"/>
+    <mergeCell ref="I152:P152"/>
     <mergeCell ref="K10:P10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="R64:V65"/>
@@ -12088,7 +12145,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="2" fitToWidth="1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader/>
-    <oddFooter>&amp;L&amp;14 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010&amp;RTiempo de retención en el punto de origen: 3 años_x000a_Tiempo de retención en archivo muerto: N/A_x000a_Medio de registro :Electrónico</oddFooter>
+    <oddFooter>&amp;L&amp;14 &amp;K00000016-HS80-8000-00010-I / 16-HS20-8000-00010</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -2146,6 +2146,56 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>95250</colOff>
+      <row>80</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <ext cx="4381500" cy="4333875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>95250</colOff>
+      <row>80</row>
+      <rowOff>95250</rowOff>
+    </from>
+    <ext cx="4381500" cy="3305175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>

--- a/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/Validacion Maquina Segura/MS_Ampseal_Attach_Gecko.xlsx
@@ -2152,9 +2152,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>11</col>
       <colOff>95250</colOff>
-      <row>80</row>
+      <row>98</row>
       <rowOff>95250</rowOff>
     </from>
     <ext cx="4381500" cy="4333875"/>
@@ -2177,9 +2177,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>1</col>
       <colOff>95250</colOff>
-      <row>80</row>
+      <row>104</row>
       <rowOff>95250</rowOff>
     </from>
     <ext cx="4381500" cy="3305175"/>
